--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run8/epoch_20/per_file_predictions_epoch_20.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run8/epoch_20/per_file_predictions_epoch_20.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="518">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="521">
   <si>
     <t>Filename</t>
   </si>
@@ -808,766 +808,775 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9326,0.0419,0.0053,0.0018</t>
-  </si>
-  <si>
-    <t>0.1045,0.0288,0.0043,0.9099</t>
-  </si>
-  <si>
-    <t>0.8231,0.0634,0.0554,0.0041</t>
-  </si>
-  <si>
-    <t>0.7784,0.0236,0.0670,0.0432</t>
-  </si>
-  <si>
-    <t>0.9918,0.0093,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9611,0.0670,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9809,0.0253,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9947,0.0056,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9844,0.0283,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9924,0.0121,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9797,0.0241,0.0007,0.0002</t>
-  </si>
-  <si>
-    <t>0.9887,0.0177,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0674,0.9037,0.0241,0.0064</t>
-  </si>
-  <si>
-    <t>0.0273,0.7014,0.5234,0.0007</t>
-  </si>
-  <si>
-    <t>0.1235,0.3466,0.5545,0.0011</t>
-  </si>
-  <si>
-    <t>0.0581,0.1915,0.8119,0.0005</t>
-  </si>
-  <si>
-    <t>0.6823,0.0580,0.1976,0.0014</t>
-  </si>
-  <si>
-    <t>0.0002,0.9991,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.0061,0.9885,0.0019,0.0000</t>
-  </si>
-  <si>
-    <t>0.0136,0.9810,0.0019,0.0001</t>
-  </si>
-  <si>
-    <t>0.0063,0.9911,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9989,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.7422,0.0321,0.1808,0.0029</t>
-  </si>
-  <si>
-    <t>0.4371,0.2418,0.1729,0.0101</t>
-  </si>
-  <si>
-    <t>0.0211,0.1309,0.9287,0.0016</t>
-  </si>
-  <si>
-    <t>0.4119,0.0602,0.4397,0.0053</t>
-  </si>
-  <si>
-    <t>0.0564,0.0548,0.8845,0.0009</t>
-  </si>
-  <si>
-    <t>0.2225,0.0448,0.7177,0.0035</t>
-  </si>
-  <si>
-    <t>0.0880,0.0057,0.9083,0.0023</t>
-  </si>
-  <si>
-    <t>0.0147,0.9804,0.0022,0.0005</t>
-  </si>
-  <si>
-    <t>0.6891,0.1785,0.0563,0.0010</t>
-  </si>
-  <si>
-    <t>0.0001,0.0107,0.9993,0.0006</t>
-  </si>
-  <si>
-    <t>0.0002,0.9983,0.0025,0.0000</t>
-  </si>
-  <si>
-    <t>0.8690,0.1240,0.0063,0.0007</t>
-  </si>
-  <si>
-    <t>0.4593,0.4345,0.0534,0.0028</t>
-  </si>
-  <si>
-    <t>0.1945,0.8284,0.0046,0.0004</t>
-  </si>
-  <si>
-    <t>0.0008,0.9980,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9994,0.0032,0.0002</t>
-  </si>
-  <si>
-    <t>0.0043,0.9433,0.2069,0.0015</t>
-  </si>
-  <si>
-    <t>0.0163,0.9009,0.1870,0.0013</t>
-  </si>
-  <si>
-    <t>0.3007,0.0175,0.7189,0.0021</t>
-  </si>
-  <si>
-    <t>0.0026,0.9650,0.1483,0.0006</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0041,0.7246,0.8961,0.0005</t>
-  </si>
-  <si>
-    <t>0.0326,0.9437,0.0040,0.1364</t>
-  </si>
-  <si>
-    <t>0.0001,0.9994,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9994,0.0003,0.0000</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0,1,0,1</t>
+  </si>
+  <si>
+    <t>0.8936,0.0554,0.0154,0.0023</t>
+  </si>
+  <si>
+    <t>0.0266,0.0062,0.0022,0.9857</t>
+  </si>
+  <si>
+    <t>0.8846,0.0129,0.0611,0.0026</t>
+  </si>
+  <si>
+    <t>0.5718,0.0711,0.0121,0.1672</t>
+  </si>
+  <si>
+    <t>0.9908,0.0120,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9915,0.0124,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9758,0.0369,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9945,0.0067,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9288,0.1187,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.9896,0.0162,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9846,0.0199,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9957,0.0051,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.1003,0.8752,0.0105,0.0011</t>
+  </si>
+  <si>
+    <t>0.1326,0.1831,0.6515,0.0010</t>
+  </si>
+  <si>
+    <t>0.5213,0.0643,0.3645,0.0015</t>
+  </si>
+  <si>
+    <t>0.0593,0.7874,0.1369,0.0008</t>
+  </si>
+  <si>
+    <t>0.6258,0.0749,0.2365,0.0036</t>
+  </si>
+  <si>
+    <t>0.0005,0.9982,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.0042,0.9924,0.0010,0.0000</t>
+  </si>
+  <si>
+    <t>0.0124,0.9833,0.0016,0.0002</t>
+  </si>
+  <si>
+    <t>0.0047,0.9925,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.0010,0.9972,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.6111,0.0251,0.3352,0.0053</t>
+  </si>
+  <si>
+    <t>0.3195,0.1605,0.4481,0.0090</t>
+  </si>
+  <si>
+    <t>0.0087,0.0783,0.9645,0.0025</t>
+  </si>
+  <si>
+    <t>0.1036,0.7213,0.1175,0.0043</t>
+  </si>
+  <si>
+    <t>0.0145,0.0164,0.9762,0.0007</t>
+  </si>
+  <si>
+    <t>0.2045,0.1020,0.6419,0.0062</t>
+  </si>
+  <si>
+    <t>0.3064,0.0078,0.7110,0.0014</t>
+  </si>
+  <si>
+    <t>0.0339,0.9624,0.0030,0.0005</t>
+  </si>
+  <si>
+    <t>0.5571,0.4356,0.0131,0.0006</t>
+  </si>
+  <si>
+    <t>0.0004,0.0337,0.9975,0.0007</t>
+  </si>
+  <si>
+    <t>0.0008,0.9955,0.0043,0.0000</t>
+  </si>
+  <si>
+    <t>0.5839,0.4708,0.0067,0.0011</t>
+  </si>
+  <si>
+    <t>0.3829,0.3761,0.1274,0.0032</t>
+  </si>
+  <si>
+    <t>0.0613,0.9287,0.0048,0.0002</t>
+  </si>
+  <si>
+    <t>0.0017,0.9951,0.0016,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.0033,0.0002</t>
+  </si>
+  <si>
+    <t>0.0102,0.8210,0.5390,0.0015</t>
+  </si>
+  <si>
+    <t>0.0137,0.9122,0.1423,0.0006</t>
+  </si>
+  <si>
+    <t>0.0509,0.1435,0.8825,0.0012</t>
+  </si>
+  <si>
+    <t>0.0043,0.9576,0.1276,0.0005</t>
   </si>
   <si>
     <t>0.0000,0.9998,0.0002,0.0000</t>
   </si>
   <si>
-    <t>0.0001,0.9725,0.7921,0.0000</t>
-  </si>
-  <si>
-    <t>0.0013,0.9665,0.2978,0.0003</t>
-  </si>
-  <si>
-    <t>0.1053,0.0718,0.7999,0.0009</t>
-  </si>
-  <si>
-    <t>0.0293,0.0407,0.9483,0.0007</t>
-  </si>
-  <si>
-    <t>0.0253,0.4806,0.8021,0.0026</t>
-  </si>
-  <si>
-    <t>0.0184,0.8633,0.2843,0.0023</t>
-  </si>
-  <si>
-    <t>0.9576,0.0601,0.0007,0.0001</t>
-  </si>
-  <si>
-    <t>0.9788,0.0181,0.0014,0.0003</t>
-  </si>
-  <si>
-    <t>0.9338,0.1026,0.0007,0.0002</t>
-  </si>
-  <si>
-    <t>0.0002,0.0247,0.9984,0.0010</t>
-  </si>
-  <si>
-    <t>0.9737,0.0290,0.0010,0.0002</t>
-  </si>
-  <si>
-    <t>0.9868,0.0205,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9109,0.1369,0.0007,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9984,0.0168,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.7986,0.9705,0.0001</t>
-  </si>
-  <si>
-    <t>0.0102,0.8704,0.3976,0.0054</t>
-  </si>
-  <si>
-    <t>0.0000,0.9986,0.1934,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.4339,0.9937,0.0001</t>
-  </si>
-  <si>
-    <t>0.0013,0.9967,0.0005,0.0000</t>
+    <t>0.0074,0.4896,0.9215,0.0011</t>
+  </si>
+  <si>
+    <t>0.0067,0.9704,0.0009,0.3516</t>
+  </si>
+  <si>
+    <t>0.0003,0.9984,0.0010,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9994,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9995,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9070,0.8855,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9959,0.0381,0.0002</t>
+  </si>
+  <si>
+    <t>0.0565,0.1590,0.8170,0.0015</t>
+  </si>
+  <si>
+    <t>0.0417,0.0212,0.9430,0.0006</t>
+  </si>
+  <si>
+    <t>0.0094,0.3012,0.9184,0.0021</t>
+  </si>
+  <si>
+    <t>0.0225,0.8532,0.2386,0.0019</t>
+  </si>
+  <si>
+    <t>0.8671,0.2030,0.0011,0.0001</t>
+  </si>
+  <si>
+    <t>0.9797,0.0180,0.0012,0.0004</t>
+  </si>
+  <si>
+    <t>0.9295,0.1000,0.0011,0.0003</t>
+  </si>
+  <si>
+    <t>0.0010,0.0946,0.9925,0.0013</t>
+  </si>
+  <si>
+    <t>0.9485,0.0627,0.0014,0.0003</t>
+  </si>
+  <si>
+    <t>0.9711,0.0431,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9120,0.1275,0.0010,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9982,0.0830,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.7384,0.9762,0.0001</t>
+  </si>
+  <si>
+    <t>0.0121,0.9369,0.0953,0.0088</t>
+  </si>
+  <si>
+    <t>0.0000,0.9991,0.0287,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.6471,0.9801,0.0001</t>
+  </si>
+  <si>
+    <t>0.0017,0.9960,0.0006,0.0000</t>
   </si>
   <si>
     <t>0.0000,1.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.8297,0.0246,0.1074,0.0009</t>
-  </si>
-  <si>
-    <t>0.1811,0.4936,0.2386,0.0013</t>
-  </si>
-  <si>
-    <t>0.0014,0.3030,0.9834,0.0008</t>
-  </si>
-  <si>
-    <t>0.0000,0.9994,0.0475,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9978,0.0057,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9996,0.0067,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.0019,0.0000</t>
-  </si>
-  <si>
-    <t>0.4801,0.0218,0.0135,0.3420</t>
-  </si>
-  <si>
-    <t>0.0029,0.0080,0.0006,0.9980</t>
-  </si>
-  <si>
-    <t>0.0295,0.0639,0.0012,0.9792</t>
-  </si>
-  <si>
-    <t>0.0195,0.0613,0.0014,0.9844</t>
-  </si>
-  <si>
-    <t>0.0256,0.0282,0.0033,0.9812</t>
-  </si>
-  <si>
-    <t>0.0047,0.0353,0.0003,0.9968</t>
-  </si>
-  <si>
-    <t>0.0000,0.9997,0.0009,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9989,0.1017,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9951,0.2232,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9987,0.0118,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.0034,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9955,0.0861,0.0000</t>
-  </si>
-  <si>
-    <t>0.9872,0.0197,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9377,0.0918,0.0008,0.0002</t>
-  </si>
-  <si>
-    <t>0.8829,0.1927,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.8987,0.1533,0.0008,0.0002</t>
-  </si>
-  <si>
-    <t>0.9782,0.0390,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9521,0.0757,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.9592,0.0708,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9813,0.0247,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.9859,0.0164,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.9954,0.0059,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9974,0.0026,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9957,0.0043,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9903,0.0156,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9786,0.0324,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9879,0.0148,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9897,0.0079,0.0008,0.0002</t>
-  </si>
-  <si>
-    <t>0.0003,0.0734,0.9977,0.0001</t>
-  </si>
-  <si>
-    <t>0.1421,0.1451,0.6689,0.0009</t>
-  </si>
-  <si>
-    <t>0.8653,0.0095,0.1013,0.0007</t>
-  </si>
-  <si>
-    <t>0.1104,0.0421,0.8557,0.0003</t>
-  </si>
-  <si>
-    <t>0.0017,0.9971,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0028,0.9952,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0047,0.9928,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0063,0.9882,0.0019,0.0001</t>
-  </si>
-  <si>
-    <t>0.0005,0.9981,0.0008,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9994,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.1285,0.8901,0.0027,0.0001</t>
-  </si>
-  <si>
-    <t>0.0463,0.9365,0.0130,0.0048</t>
-  </si>
-  <si>
-    <t>0.3233,0.1565,0.4037,0.0021</t>
-  </si>
-  <si>
-    <t>0.4060,0.4087,0.0889,0.0033</t>
-  </si>
-  <si>
-    <t>0.1613,0.7964,0.0270,0.0047</t>
-  </si>
-  <si>
-    <t>0.0594,0.8760,0.0043,0.1014</t>
+    <t>0.3471,0.4134,0.1359,0.0018</t>
+  </si>
+  <si>
+    <t>0.0852,0.8715,0.0236,0.0014</t>
+  </si>
+  <si>
+    <t>0.0023,0.4075,0.9679,0.0008</t>
+  </si>
+  <si>
+    <t>0.0000,0.9989,0.0477,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9990,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9997,0.0047,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.0041,0.0000</t>
+  </si>
+  <si>
+    <t>0.7640,0.0222,0.0726,0.0527</t>
+  </si>
+  <si>
+    <t>0.0014,0.0047,0.0003,0.9991</t>
+  </si>
+  <si>
+    <t>0.0560,0.0257,0.0016,0.9652</t>
+  </si>
+  <si>
+    <t>0.0402,0.0385,0.0028,0.9729</t>
+  </si>
+  <si>
+    <t>0.0276,0.0160,0.0048,0.9801</t>
+  </si>
+  <si>
+    <t>0.0060,0.0075,0.0007,0.9964</t>
+  </si>
+  <si>
+    <t>0.0001,0.9985,0.0053,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9977,0.0602,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.9904,0.0988,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.9948,0.1323,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9990,0.0034,0.0000</t>
+  </si>
+  <si>
+    <t>0.9472,0.0936,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.7235,0.3751,0.0010,0.0001</t>
+  </si>
+  <si>
+    <t>0.6526,0.4359,0.0021,0.0002</t>
+  </si>
+  <si>
+    <t>0.9379,0.1093,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9868,0.0191,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9638,0.0545,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.9712,0.0506,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.8278,0.2290,0.0016,0.0002</t>
+  </si>
+  <si>
+    <t>0.9932,0.0075,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9893,0.0173,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9973,0.0035,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9956,0.0046,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9949,0.0076,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9233,0.1335,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9949,0.0041,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9960,0.0038,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0033,0.0095,0.9903,0.0030</t>
+  </si>
+  <si>
+    <t>0.1588,0.2465,0.4839,0.0010</t>
+  </si>
+  <si>
+    <t>0.8756,0.0249,0.0474,0.0008</t>
+  </si>
+  <si>
+    <t>0.0671,0.0377,0.8972,0.0013</t>
+  </si>
+  <si>
+    <t>0.0016,0.9968,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0040,0.9929,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.0075,0.9901,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.0226,0.9675,0.0036,0.0001</t>
+  </si>
+  <si>
+    <t>0.0009,0.9974,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.9983,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.1924,0.8446,0.0032,0.0001</t>
+  </si>
+  <si>
+    <t>0.2818,0.7213,0.0110,0.0014</t>
+  </si>
+  <si>
+    <t>0.6340,0.0380,0.3024,0.0013</t>
+  </si>
+  <si>
+    <t>0.2329,0.7171,0.0216,0.0025</t>
+  </si>
+  <si>
+    <t>0.0811,0.8360,0.0775,0.0054</t>
+  </si>
+  <si>
+    <t>0.3488,0.3947,0.0095,0.1854</t>
   </si>
   <si>
     <t>0.0000,0.9997,0.0002,0.0000</t>
   </si>
   <si>
-    <t>0.0005,0.9980,0.0010,0.0008</t>
-  </si>
-  <si>
-    <t>0.0000,0.9997,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.0009,0.9974,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.1653,0.8301,0.0079,0.0002</t>
-  </si>
-  <si>
-    <t>0.2933,0.7299,0.0082,0.0003</t>
-  </si>
-  <si>
-    <t>0.5565,0.5706,0.0008,0.0003</t>
-  </si>
-  <si>
-    <t>0.9843,0.0095,0.0016,0.0003</t>
-  </si>
-  <si>
-    <t>0.9875,0.0131,0.0005,0.0003</t>
-  </si>
-  <si>
-    <t>0.9651,0.0200,0.0045,0.0005</t>
-  </si>
-  <si>
-    <t>0.9950,0.0052,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.6405,0.5010,0.0009,0.0005</t>
-  </si>
-  <si>
-    <t>0.9846,0.0126,0.0011,0.0003</t>
-  </si>
-  <si>
-    <t>0.9882,0.0113,0.0006,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.9905,0.3812,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.9779,0.3061,0.0001</t>
-  </si>
-  <si>
-    <t>0.0008,0.9853,0.0858,0.0001</t>
-  </si>
-  <si>
-    <t>0.0081,0.9499,0.0844,0.0006</t>
-  </si>
-  <si>
-    <t>0.8341,0.1129,0.0117,0.0044</t>
-  </si>
-  <si>
-    <t>0.3644,0.4681,0.0762,0.0039</t>
-  </si>
-  <si>
-    <t>0.7632,0.0367,0.1488,0.0012</t>
-  </si>
-  <si>
-    <t>0.5815,0.1864,0.1246,0.0017</t>
-  </si>
-  <si>
-    <t>0.6609,0.0110,0.0052,0.2248</t>
-  </si>
-  <si>
-    <t>0.0000,0.0003,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0008,0.1696,0.0001,0.9988</t>
-  </si>
-  <si>
-    <t>0.0238,0.0073,0.0020,0.9869</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0075,0.0000</t>
-  </si>
-  <si>
-    <t>0.9918,0.0067,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.0398,0.9693,0.0006,0.0007</t>
-  </si>
-  <si>
-    <t>0.9451,0.0485,0.0035,0.0006</t>
-  </si>
-  <si>
-    <t>0.1002,0.9196,0.0015,0.0002</t>
-  </si>
-  <si>
-    <t>0.9400,0.0455,0.0052,0.0007</t>
-  </si>
-  <si>
-    <t>0.8753,0.0517,0.0312,0.0019</t>
-  </si>
-  <si>
-    <t>0.9894,0.0061,0.0011,0.0003</t>
-  </si>
-  <si>
-    <t>0.0007,0.3299,0.9906,0.0004</t>
-  </si>
-  <si>
-    <t>0.9757,0.0023,0.0081,0.0004</t>
-  </si>
-  <si>
-    <t>0.9551,0.0248,0.0058,0.0004</t>
-  </si>
-  <si>
-    <t>0.0519,0.9254,0.0131,0.0010</t>
-  </si>
-  <si>
-    <t>0.6764,0.3965,0.0037,0.0008</t>
-  </si>
-  <si>
-    <t>0.6064,0.3735,0.0243,0.0017</t>
-  </si>
-  <si>
-    <t>0.0146,0.9724,0.0070,0.0004</t>
-  </si>
-  <si>
-    <t>0.4076,0.5724,0.0194,0.0011</t>
-  </si>
-  <si>
-    <t>0.3406,0.7258,0.0038,0.0014</t>
-  </si>
-  <si>
-    <t>0.9851,0.0165,0.0006,0.0002</t>
-  </si>
-  <si>
-    <t>0.9938,0.0070,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9663,0.0280,0.0026,0.0006</t>
-  </si>
-  <si>
-    <t>0.9859,0.0081,0.0017,0.0005</t>
-  </si>
-  <si>
-    <t>0.9768,0.0201,0.0015,0.0003</t>
-  </si>
-  <si>
-    <t>0.9871,0.0156,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9861,0.0163,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.9918,0.0080,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.0361,0.9667,0.0010,0.0001</t>
-  </si>
-  <si>
-    <t>0.1608,0.8654,0.0024,0.0003</t>
-  </si>
-  <si>
-    <t>0.3890,0.6829,0.0023,0.0001</t>
-  </si>
-  <si>
-    <t>0.4684,0.6475,0.0016,0.0001</t>
-  </si>
-  <si>
-    <t>0.8938,0.1623,0.0007,0.0002</t>
-  </si>
-  <si>
-    <t>0.9292,0.0945,0.0012,0.0005</t>
-  </si>
-  <si>
-    <t>0.9018,0.1106,0.0035,0.0003</t>
-  </si>
-  <si>
-    <t>0.8936,0.1180,0.0049,0.0005</t>
-  </si>
-  <si>
-    <t>0.0002,0.1036,0.9982,0.0001</t>
-  </si>
-  <si>
-    <t>0.7275,0.1992,0.0428,0.0016</t>
-  </si>
-  <si>
-    <t>0.0008,0.7121,0.9553,0.0001</t>
-  </si>
-  <si>
-    <t>0.0036,0.8533,0.7590,0.0006</t>
-  </si>
-  <si>
-    <t>0.0810,0.1570,0.7866,0.0013</t>
-  </si>
-  <si>
-    <t>0.0001,0.9795,0.7695,0.0000</t>
-  </si>
-  <si>
-    <t>0.0075,0.5300,0.8920,0.0004</t>
-  </si>
-  <si>
-    <t>0.1145,0.0083,0.9127,0.0003</t>
-  </si>
-  <si>
-    <t>0.0396,0.2539,0.7901,0.0011</t>
-  </si>
-  <si>
-    <t>0.0328,0.8418,0.2346,0.0016</t>
-  </si>
-  <si>
-    <t>0.0389,0.7230,0.4533,0.0027</t>
-  </si>
-  <si>
-    <t>0.0761,0.8971,0.0146,0.0006</t>
-  </si>
-  <si>
-    <t>0.2565,0.5548,0.1317,0.0036</t>
-  </si>
-  <si>
-    <t>0.0237,0.9084,0.0935,0.0007</t>
-  </si>
-  <si>
-    <t>0.0403,0.9362,0.0143,0.0010</t>
-  </si>
-  <si>
-    <t>0.0891,0.8841,0.0178,0.0025</t>
-  </si>
-  <si>
-    <t>0.1239,0.7936,0.0436,0.0012</t>
-  </si>
-  <si>
-    <t>0.0954,0.9242,0.0013,0.0002</t>
-  </si>
-  <si>
-    <t>0.1491,0.8827,0.0015,0.0001</t>
-  </si>
-  <si>
-    <t>0.1687,0.8767,0.0010,0.0001</t>
-  </si>
-  <si>
-    <t>0.3661,0.7480,0.0007,0.0002</t>
-  </si>
-  <si>
-    <t>0.0864,0.9377,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.0865,0.8924,0.0137,0.0013</t>
-  </si>
-  <si>
-    <t>0.8299,0.0515,0.0516,0.0013</t>
-  </si>
-  <si>
-    <t>0.6954,0.1671,0.0452,0.0070</t>
-  </si>
-  <si>
-    <t>0.6088,0.1306,0.1695,0.0044</t>
-  </si>
-  <si>
-    <t>0.5081,0.0753,0.3722,0.0037</t>
-  </si>
-  <si>
-    <t>0.0020,0.2192,0.9724,0.0019</t>
-  </si>
-  <si>
-    <t>0.0254,0.9174,0.0723,0.0023</t>
-  </si>
-  <si>
-    <t>0.0045,0.8597,0.6998,0.0007</t>
-  </si>
-  <si>
-    <t>0.0102,0.9512,0.0535,0.0004</t>
-  </si>
-  <si>
-    <t>0.0006,0.9876,0.0613,0.0010</t>
-  </si>
-  <si>
-    <t>0.9881,0.0166,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9879,0.0135,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.8543,0.2475,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.9292,0.1221,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9694,0.0459,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9957,0.0042,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9662,0.0460,0.0007,0.0003</t>
-  </si>
-  <si>
-    <t>0.9908,0.0118,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0237,0.1111,0.9406,0.0011</t>
-  </si>
-  <si>
-    <t>0.0306,0.9554,0.0063,0.0004</t>
-  </si>
-  <si>
-    <t>0.6320,0.3139,0.0328,0.0056</t>
-  </si>
-  <si>
-    <t>0.0203,0.4910,0.8028,0.0005</t>
-  </si>
-  <si>
-    <t>0.0010,0.8397,0.8741,0.0005</t>
-  </si>
-  <si>
-    <t>0.0081,0.8652,0.4441,0.0004</t>
-  </si>
-  <si>
-    <t>0.0016,0.1567,0.9865,0.0004</t>
-  </si>
-  <si>
-    <t>0.0585,0.3027,0.7014,0.0069</t>
-  </si>
-  <si>
-    <t>0.0001,0.6288,0.9923,0.0000</t>
-  </si>
-  <si>
-    <t>0.0078,0.9386,0.1283,0.0042</t>
-  </si>
-  <si>
-    <t>0.0183,0.7472,0.6076,0.0013</t>
-  </si>
-  <si>
-    <t>0.4361,0.4556,0.0404,0.0035</t>
-  </si>
-  <si>
-    <t>0.7146,0.0184,0.2599,0.0019</t>
-  </si>
-  <si>
-    <t>0.8908,0.0628,0.0101,0.0011</t>
-  </si>
-  <si>
-    <t>0.9450,0.0955,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9738,0.0389,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.9866,0.0166,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9793,0.0253,0.0006,0.0002</t>
-  </si>
-  <si>
-    <t>0.9915,0.0126,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9394,0.0876,0.0008,0.0002</t>
-  </si>
-  <si>
-    <t>0.8390,0.2745,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9575,0.0672,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.1402,0.6016,0.1881,0.0017</t>
-  </si>
-  <si>
-    <t>0.0006,0.8192,0.9553,0.0001</t>
-  </si>
-  <si>
-    <t>0.0023,0.9586,0.2513,0.0007</t>
-  </si>
-  <si>
-    <t>0.0048,0.9661,0.0840,0.0010</t>
-  </si>
-  <si>
-    <t>0.0138,0.6522,0.7810,0.0014</t>
-  </si>
-  <si>
-    <t>0.3371,0.1625,0.3848,0.0176</t>
-  </si>
-  <si>
-    <t>0.2788,0.3624,0.2014,0.0058</t>
-  </si>
-  <si>
-    <t>0.1066,0.1778,0.7215,0.0055</t>
-  </si>
-  <si>
-    <t>0.9074,0.0409,0.0196,0.0026</t>
-  </si>
-  <si>
-    <t>0.0426,0.1174,0.0026,0.9530</t>
-  </si>
-  <si>
-    <t>0.2278,0.1170,0.0017,0.6802</t>
-  </si>
-  <si>
-    <t>0.0030,0.0012,0.0006,0.9984</t>
-  </si>
-  <si>
-    <t>0.0008,0.0004,0.0002,0.9995</t>
-  </si>
-  <si>
-    <t>0.7419,0.1758,0.0288,0.0113</t>
+    <t>0.0000,0.9999,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.9986,0.0007,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0014,0.9962,0.0009,0.0000</t>
+  </si>
+  <si>
+    <t>0.2507,0.7412,0.0128,0.0003</t>
+  </si>
+  <si>
+    <t>0.3152,0.7538,0.0025,0.0002</t>
+  </si>
+  <si>
+    <t>0.3434,0.7438,0.0011,0.0002</t>
+  </si>
+  <si>
+    <t>0.9779,0.0166,0.0019,0.0006</t>
+  </si>
+  <si>
+    <t>0.9884,0.0134,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9611,0.0292,0.0032,0.0004</t>
+  </si>
+  <si>
+    <t>0.9971,0.0021,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.6410,0.4838,0.0009,0.0002</t>
+  </si>
+  <si>
+    <t>0.9733,0.0263,0.0015,0.0004</t>
+  </si>
+  <si>
+    <t>0.9911,0.0064,0.0007,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.9775,0.7916,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9771,0.7145,0.0000</t>
+  </si>
+  <si>
+    <t>0.0035,0.9602,0.1381,0.0001</t>
+  </si>
+  <si>
+    <t>0.0060,0.9145,0.3348,0.0004</t>
+  </si>
+  <si>
+    <t>0.8612,0.0587,0.0204,0.0031</t>
+  </si>
+  <si>
+    <t>0.6660,0.0858,0.1614,0.0021</t>
+  </si>
+  <si>
+    <t>0.1889,0.0600,0.7774,0.0020</t>
+  </si>
+  <si>
+    <t>0.2533,0.7444,0.0125,0.0028</t>
+  </si>
+  <si>
+    <t>0.6271,0.0100,0.0020,0.2631</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0015,0.0649,0.0001,0.9987</t>
+  </si>
+  <si>
+    <t>0.0144,0.0062,0.0030,0.9905</t>
+  </si>
+  <si>
+    <t>0.0000,0.9997,0.0688,0.0000</t>
+  </si>
+  <si>
+    <t>0.9928,0.0065,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.0155,0.9865,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.9837,0.0105,0.0017,0.0004</t>
+  </si>
+  <si>
+    <t>0.1368,0.8971,0.0014,0.0004</t>
+  </si>
+  <si>
+    <t>0.9777,0.0105,0.0027,0.0003</t>
+  </si>
+  <si>
+    <t>0.9123,0.0480,0.0137,0.0030</t>
+  </si>
+  <si>
+    <t>0.9824,0.0073,0.0027,0.0003</t>
+  </si>
+  <si>
+    <t>0.0007,0.2234,0.9921,0.0007</t>
+  </si>
+  <si>
+    <t>0.9592,0.0048,0.0118,0.0019</t>
+  </si>
+  <si>
+    <t>0.8663,0.1446,0.0053,0.0006</t>
+  </si>
+  <si>
+    <t>0.1230,0.8559,0.0107,0.0006</t>
+  </si>
+  <si>
+    <t>0.9082,0.0971,0.0035,0.0010</t>
+  </si>
+  <si>
+    <t>0.3084,0.6922,0.0175,0.0021</t>
+  </si>
+  <si>
+    <t>0.0166,0.9751,0.0031,0.0003</t>
+  </si>
+  <si>
+    <t>0.1992,0.8186,0.0077,0.0019</t>
+  </si>
+  <si>
+    <t>0.6154,0.4588,0.0030,0.0009</t>
+  </si>
+  <si>
+    <t>0.9684,0.0361,0.0011,0.0003</t>
+  </si>
+  <si>
+    <t>0.9955,0.0044,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9686,0.0335,0.0014,0.0004</t>
+  </si>
+  <si>
+    <t>0.9909,0.0066,0.0007,0.0003</t>
+  </si>
+  <si>
+    <t>0.9840,0.0149,0.0010,0.0004</t>
+  </si>
+  <si>
+    <t>0.9848,0.0184,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9507,0.0428,0.0033,0.0005</t>
+  </si>
+  <si>
+    <t>0.9929,0.0052,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.0453,0.9589,0.0010,0.0001</t>
+  </si>
+  <si>
+    <t>0.1673,0.8615,0.0020,0.0002</t>
+  </si>
+  <si>
+    <t>0.1653,0.8654,0.0022,0.0001</t>
+  </si>
+  <si>
+    <t>0.0799,0.8296,0.0643,0.0007</t>
+  </si>
+  <si>
+    <t>0.9523,0.0614,0.0008,0.0001</t>
+  </si>
+  <si>
+    <t>0.8866,0.1298,0.0042,0.0008</t>
+  </si>
+  <si>
+    <t>0.9512,0.0436,0.0030,0.0003</t>
+  </si>
+  <si>
+    <t>0.6564,0.4323,0.0036,0.0002</t>
+  </si>
+  <si>
+    <t>0.0002,0.3592,0.9966,0.0000</t>
+  </si>
+  <si>
+    <t>0.6906,0.3047,0.0199,0.0011</t>
+  </si>
+  <si>
+    <t>0.0009,0.7525,0.9450,0.0001</t>
+  </si>
+  <si>
+    <t>0.0017,0.8860,0.8140,0.0003</t>
+  </si>
+  <si>
+    <t>0.0484,0.0805,0.9037,0.0011</t>
+  </si>
+  <si>
+    <t>0.0002,0.9386,0.8879,0.0001</t>
+  </si>
+  <si>
+    <t>0.0048,0.5096,0.9425,0.0005</t>
+  </si>
+  <si>
+    <t>0.0321,0.0219,0.9504,0.0009</t>
+  </si>
+  <si>
+    <t>0.0212,0.0835,0.9508,0.0004</t>
+  </si>
+  <si>
+    <t>0.0120,0.7532,0.7485,0.0011</t>
+  </si>
+  <si>
+    <t>0.0150,0.5730,0.8512,0.0008</t>
+  </si>
+  <si>
+    <t>0.1411,0.8082,0.0193,0.0016</t>
+  </si>
+  <si>
+    <t>0.0947,0.7203,0.1428,0.0008</t>
+  </si>
+  <si>
+    <t>0.0236,0.8751,0.1731,0.0004</t>
+  </si>
+  <si>
+    <t>0.2485,0.6848,0.0241,0.0011</t>
+  </si>
+  <si>
+    <t>0.2001,0.7973,0.0118,0.0037</t>
+  </si>
+  <si>
+    <t>0.1617,0.6328,0.1302,0.0009</t>
+  </si>
+  <si>
+    <t>0.0880,0.9229,0.0017,0.0001</t>
+  </si>
+  <si>
+    <t>0.0229,0.9743,0.0012,0.0001</t>
+  </si>
+  <si>
+    <t>0.2172,0.8556,0.0008,0.0001</t>
+  </si>
+  <si>
+    <t>0.3352,0.7881,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.0866,0.9429,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.0256,0.9222,0.0587,0.0006</t>
+  </si>
+  <si>
+    <t>0.8856,0.0274,0.0298,0.0018</t>
+  </si>
+  <si>
+    <t>0.4853,0.4178,0.0328,0.0108</t>
+  </si>
+  <si>
+    <t>0.1754,0.7887,0.0337,0.0265</t>
+  </si>
+  <si>
+    <t>0.7369,0.1045,0.0582,0.0012</t>
+  </si>
+  <si>
+    <t>0.0035,0.0825,0.9825,0.0014</t>
+  </si>
+  <si>
+    <t>0.0295,0.8503,0.2277,0.0023</t>
+  </si>
+  <si>
+    <t>0.0034,0.9239,0.4670,0.0005</t>
+  </si>
+  <si>
+    <t>0.0487,0.8164,0.1552,0.0012</t>
+  </si>
+  <si>
+    <t>0.0002,0.9974,0.0053,0.0002</t>
+  </si>
+  <si>
+    <t>0.9564,0.0645,0.0006,0.0002</t>
+  </si>
+  <si>
+    <t>0.9859,0.0143,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.9402,0.1092,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9899,0.0140,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9385,0.0863,0.0009,0.0002</t>
+  </si>
+  <si>
+    <t>0.9846,0.0161,0.0006,0.0002</t>
+  </si>
+  <si>
+    <t>0.9898,0.0115,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9409,0.0742,0.0015,0.0003</t>
+  </si>
+  <si>
+    <t>0.0158,0.5312,0.8276,0.0005</t>
+  </si>
+  <si>
+    <t>0.0496,0.9070,0.0276,0.0004</t>
+  </si>
+  <si>
+    <t>0.7813,0.1355,0.0450,0.0050</t>
+  </si>
+  <si>
+    <t>0.0014,0.3926,0.9800,0.0001</t>
+  </si>
+  <si>
+    <t>0.0008,0.9131,0.7706,0.0004</t>
+  </si>
+  <si>
+    <t>0.0069,0.9414,0.1518,0.0009</t>
+  </si>
+  <si>
+    <t>0.0008,0.1285,0.9923,0.0003</t>
+  </si>
+  <si>
+    <t>0.0354,0.8233,0.1873,0.0014</t>
+  </si>
+  <si>
+    <t>0.0001,0.5698,0.9925,0.0000</t>
+  </si>
+  <si>
+    <t>0.0535,0.4920,0.5862,0.0025</t>
+  </si>
+  <si>
+    <t>0.0074,0.9055,0.3199,0.0010</t>
+  </si>
+  <si>
+    <t>0.4289,0.5148,0.0213,0.0042</t>
+  </si>
+  <si>
+    <t>0.4403,0.1835,0.2111,0.0017</t>
+  </si>
+  <si>
+    <t>0.8690,0.0871,0.0085,0.0007</t>
+  </si>
+  <si>
+    <t>0.8868,0.1868,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.9471,0.0758,0.0008,0.0002</t>
+  </si>
+  <si>
+    <t>0.9931,0.0080,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.8653,0.1979,0.0016,0.0003</t>
+  </si>
+  <si>
+    <t>0.9876,0.0165,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9266,0.1167,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.4333,0.6939,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9688,0.0488,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.0701,0.7815,0.1636,0.0023</t>
+  </si>
+  <si>
+    <t>0.0001,0.9115,0.9567,0.0000</t>
+  </si>
+  <si>
+    <t>0.0023,0.8016,0.8754,0.0003</t>
+  </si>
+  <si>
+    <t>0.0024,0.9876,0.0167,0.0004</t>
+  </si>
+  <si>
+    <t>0.1161,0.0443,0.8265,0.0045</t>
+  </si>
+  <si>
+    <t>0.1112,0.2574,0.6667,0.0097</t>
+  </si>
+  <si>
+    <t>0.5950,0.0620,0.2947,0.0028</t>
+  </si>
+  <si>
+    <t>0.0411,0.6764,0.4657,0.0069</t>
+  </si>
+  <si>
+    <t>0.9222,0.0476,0.0093,0.0021</t>
+  </si>
+  <si>
+    <t>0.0188,0.5095,0.0006,0.9413</t>
+  </si>
+  <si>
+    <t>0.0220,0.2426,0.0005,0.9692</t>
+  </si>
+  <si>
+    <t>0.0012,0.0008,0.0001,0.9994</t>
+  </si>
+  <si>
+    <t>0.0015,0.0006,0.0003,0.9992</t>
+  </si>
+  <si>
+    <t>0.8036,0.1069,0.0273,0.0067</t>
   </si>
 </sst>
 </file>
@@ -1953,7 +1962,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1967,7 +1976,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1981,7 +1990,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1995,7 +2004,7 @@
         <v>259</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2009,7 +2018,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2023,7 +2032,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2037,7 +2046,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2051,7 +2060,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2065,7 +2074,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2079,7 +2088,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2093,7 +2102,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2107,7 +2116,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2121,7 +2130,7 @@
         <v>262</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2132,10 +2141,10 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2146,10 +2155,10 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D16" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2160,10 +2169,10 @@
         <v>261</v>
       </c>
       <c r="C17" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2177,7 +2186,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2191,7 +2200,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2205,7 +2214,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2219,7 +2228,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2233,7 +2242,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2247,7 +2256,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2261,7 +2270,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2272,10 +2281,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D25" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2289,7 +2298,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2300,10 +2309,10 @@
         <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2317,7 +2326,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2331,7 +2340,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2345,7 +2354,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2359,7 +2368,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2373,7 +2382,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2387,7 +2396,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2401,7 +2410,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2415,7 +2424,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2426,10 +2435,10 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D36" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2443,7 +2452,7 @@
         <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2457,7 +2466,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2471,7 +2480,7 @@
         <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2482,10 +2491,10 @@
         <v>261</v>
       </c>
       <c r="C40" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D40" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2499,7 +2508,7 @@
         <v>262</v>
       </c>
       <c r="D41" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2513,7 +2522,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2527,7 +2536,7 @@
         <v>262</v>
       </c>
       <c r="D43" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2541,7 +2550,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2552,10 +2561,10 @@
         <v>261</v>
       </c>
       <c r="C45" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2569,7 +2578,7 @@
         <v>262</v>
       </c>
       <c r="D46" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2583,7 +2592,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2597,7 +2606,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2611,7 +2620,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2625,7 +2634,7 @@
         <v>263</v>
       </c>
       <c r="D50" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2639,7 +2648,7 @@
         <v>262</v>
       </c>
       <c r="D51" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2653,7 +2662,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2667,7 +2676,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2681,7 +2690,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2695,7 +2704,7 @@
         <v>262</v>
       </c>
       <c r="D55" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2709,7 +2718,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2723,7 +2732,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2737,7 +2746,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2751,7 +2760,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2765,7 +2774,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2779,7 +2788,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2793,7 +2802,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2807,7 +2816,7 @@
         <v>262</v>
       </c>
       <c r="D63" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2821,7 +2830,7 @@
         <v>263</v>
       </c>
       <c r="D64" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2835,7 +2844,7 @@
         <v>262</v>
       </c>
       <c r="D65" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2849,7 +2858,7 @@
         <v>262</v>
       </c>
       <c r="D66" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2860,10 +2869,10 @@
         <v>261</v>
       </c>
       <c r="C67" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D67" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2877,7 +2886,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2891,7 +2900,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2902,10 +2911,10 @@
         <v>259</v>
       </c>
       <c r="C70" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D70" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2916,10 +2925,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D71" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2933,7 +2942,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2947,7 +2956,7 @@
         <v>262</v>
       </c>
       <c r="D73" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2961,7 +2970,7 @@
         <v>262</v>
       </c>
       <c r="D74" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2975,7 +2984,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2989,7 +2998,7 @@
         <v>262</v>
       </c>
       <c r="D76" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3003,7 +3012,7 @@
         <v>259</v>
       </c>
       <c r="D77" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3017,7 +3026,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3031,7 +3040,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3045,7 +3054,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3059,7 +3068,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3073,7 +3082,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3087,7 +3096,7 @@
         <v>262</v>
       </c>
       <c r="D83" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3101,7 +3110,7 @@
         <v>262</v>
       </c>
       <c r="D84" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3115,7 +3124,7 @@
         <v>262</v>
       </c>
       <c r="D85" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3129,7 +3138,7 @@
         <v>262</v>
       </c>
       <c r="D86" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3143,7 +3152,7 @@
         <v>262</v>
       </c>
       <c r="D87" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3157,7 +3166,7 @@
         <v>262</v>
       </c>
       <c r="D88" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3171,7 +3180,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3185,7 +3194,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3199,7 +3208,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3213,7 +3222,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3227,7 +3236,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3241,7 +3250,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3255,7 +3264,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3269,7 +3278,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3283,7 +3292,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3297,7 +3306,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3311,7 +3320,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3325,7 +3334,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3339,7 +3348,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3353,7 +3362,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3367,7 +3376,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3381,7 +3390,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3395,7 +3404,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3406,10 +3415,10 @@
         <v>261</v>
       </c>
       <c r="C106" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D106" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3423,7 +3432,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3437,7 +3446,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3451,7 +3460,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3465,7 +3474,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3479,7 +3488,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3493,7 +3502,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3507,7 +3516,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3521,7 +3530,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3535,7 +3544,7 @@
         <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3549,7 +3558,7 @@
         <v>262</v>
       </c>
       <c r="D116" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3563,7 +3572,7 @@
         <v>259</v>
       </c>
       <c r="D117" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3574,10 +3583,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D118" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3591,7 +3600,7 @@
         <v>262</v>
       </c>
       <c r="D119" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3602,10 +3611,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D120" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3619,7 +3628,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>306</v>
+        <v>385</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3633,7 +3642,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3647,7 +3656,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3661,7 +3670,7 @@
         <v>262</v>
       </c>
       <c r="D124" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3675,7 +3684,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3689,7 +3698,7 @@
         <v>262</v>
       </c>
       <c r="D126" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3703,7 +3712,7 @@
         <v>262</v>
       </c>
       <c r="D127" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3717,7 +3726,7 @@
         <v>262</v>
       </c>
       <c r="D128" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3731,7 +3740,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3745,7 +3754,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3759,7 +3768,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3773,7 +3782,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3784,10 +3793,10 @@
         <v>259</v>
       </c>
       <c r="C133" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3801,7 +3810,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3815,7 +3824,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3826,10 +3835,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3840,10 +3849,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3857,7 +3866,7 @@
         <v>262</v>
       </c>
       <c r="D138" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3871,7 +3880,7 @@
         <v>262</v>
       </c>
       <c r="D139" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3885,7 +3894,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3899,7 +3908,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3910,10 +3919,10 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3924,10 +3933,10 @@
         <v>259</v>
       </c>
       <c r="C143" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D143" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3941,7 +3950,7 @@
         <v>259</v>
       </c>
       <c r="D144" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3955,7 +3964,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3969,7 +3978,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3983,7 +3992,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3997,7 +4006,7 @@
         <v>262</v>
       </c>
       <c r="D148" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4011,7 +4020,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4025,7 +4034,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4039,7 +4048,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4053,7 +4062,7 @@
         <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4067,7 +4076,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4081,7 +4090,7 @@
         <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4095,7 +4104,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4109,7 +4118,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4123,7 +4132,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4137,7 +4146,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4151,7 +4160,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4165,7 +4174,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4176,10 +4185,10 @@
         <v>259</v>
       </c>
       <c r="C161" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D161" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4193,7 +4202,7 @@
         <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4207,7 +4216,7 @@
         <v>262</v>
       </c>
       <c r="D163" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4218,10 +4227,10 @@
         <v>259</v>
       </c>
       <c r="C164" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4235,7 +4244,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4249,7 +4258,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4263,7 +4272,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4277,7 +4286,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4291,7 +4300,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4305,7 +4314,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4319,7 +4328,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4333,7 +4342,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4347,7 +4356,7 @@
         <v>262</v>
       </c>
       <c r="D173" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4361,7 +4370,7 @@
         <v>262</v>
       </c>
       <c r="D174" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4375,7 +4384,7 @@
         <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4389,7 +4398,7 @@
         <v>262</v>
       </c>
       <c r="D176" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4403,7 +4412,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4417,7 +4426,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4431,7 +4440,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4445,7 +4454,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4459,7 +4468,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4473,7 +4482,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4487,7 +4496,7 @@
         <v>263</v>
       </c>
       <c r="D183" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4501,7 +4510,7 @@
         <v>263</v>
       </c>
       <c r="D184" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4515,7 +4524,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4529,7 +4538,7 @@
         <v>263</v>
       </c>
       <c r="D186" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4543,7 +4552,7 @@
         <v>263</v>
       </c>
       <c r="D187" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4557,7 +4566,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4571,7 +4580,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4582,10 +4591,10 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D190" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4596,10 +4605,10 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D191" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4613,7 +4622,7 @@
         <v>262</v>
       </c>
       <c r="D192" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4627,7 +4636,7 @@
         <v>262</v>
       </c>
       <c r="D193" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4641,7 +4650,7 @@
         <v>262</v>
       </c>
       <c r="D194" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4655,7 +4664,7 @@
         <v>262</v>
       </c>
       <c r="D195" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4669,7 +4678,7 @@
         <v>262</v>
       </c>
       <c r="D196" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4683,7 +4692,7 @@
         <v>262</v>
       </c>
       <c r="D197" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4697,7 +4706,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4711,7 +4720,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4725,7 +4734,7 @@
         <v>262</v>
       </c>
       <c r="D200" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4739,7 +4748,7 @@
         <v>262</v>
       </c>
       <c r="D201" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4753,7 +4762,7 @@
         <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4767,7 +4776,7 @@
         <v>262</v>
       </c>
       <c r="D203" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4781,7 +4790,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4792,10 +4801,10 @@
         <v>259</v>
       </c>
       <c r="C205" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D205" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4806,10 +4815,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D206" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4823,7 +4832,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4837,7 +4846,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4851,7 +4860,7 @@
         <v>262</v>
       </c>
       <c r="D209" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4862,10 +4871,10 @@
         <v>261</v>
       </c>
       <c r="C210" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D210" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4879,7 +4888,7 @@
         <v>262</v>
       </c>
       <c r="D211" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4893,7 +4902,7 @@
         <v>262</v>
       </c>
       <c r="D212" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4907,7 +4916,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4921,7 +4930,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4935,7 +4944,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4949,7 +4958,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4963,7 +4972,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4977,7 +4986,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4991,7 +5000,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5005,7 +5014,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5016,10 +5025,10 @@
         <v>261</v>
       </c>
       <c r="C221" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D221" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5033,7 +5042,7 @@
         <v>262</v>
       </c>
       <c r="D222" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5047,7 +5056,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5061,7 +5070,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5075,7 +5084,7 @@
         <v>263</v>
       </c>
       <c r="D225" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5089,7 +5098,7 @@
         <v>262</v>
       </c>
       <c r="D226" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5103,7 +5112,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5114,10 +5123,10 @@
         <v>261</v>
       </c>
       <c r="C228" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D228" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5131,7 +5140,7 @@
         <v>263</v>
       </c>
       <c r="D229" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5142,10 +5151,10 @@
         <v>261</v>
       </c>
       <c r="C230" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5156,10 +5165,10 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D231" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5170,10 +5179,10 @@
         <v>259</v>
       </c>
       <c r="C232" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D232" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5184,10 +5193,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D233" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5201,7 +5210,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5215,7 +5224,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5229,7 +5238,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5243,7 +5252,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5257,7 +5266,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5271,7 +5280,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5285,7 +5294,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5296,10 +5305,10 @@
         <v>259</v>
       </c>
       <c r="C241" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D241" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5313,7 +5322,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5327,7 +5336,7 @@
         <v>262</v>
       </c>
       <c r="D243" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5341,7 +5350,7 @@
         <v>263</v>
       </c>
       <c r="D244" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5352,10 +5361,10 @@
         <v>261</v>
       </c>
       <c r="C245" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D245" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5369,7 +5378,7 @@
         <v>262</v>
       </c>
       <c r="D246" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5380,10 +5389,10 @@
         <v>261</v>
       </c>
       <c r="C247" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5394,10 +5403,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5411,7 +5420,7 @@
         <v>259</v>
       </c>
       <c r="D249" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5422,10 +5431,10 @@
         <v>261</v>
       </c>
       <c r="C250" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D250" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5439,7 +5448,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5450,10 +5459,10 @@
         <v>260</v>
       </c>
       <c r="C252" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="D252" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5467,7 +5476,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5481,7 +5490,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5495,7 +5504,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5509,7 +5518,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
     </row>
   </sheetData>
